--- a/public/plantilla-plan-emergencias.xlsx
+++ b/public/plantilla-plan-emergencias.xlsx
@@ -15,7 +15,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="41">
+  <numFmts count="0"/>
+  <fonts count="43">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -305,6 +306,15 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="20">
@@ -1033,7 +1043,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="366">
+  <cellXfs count="378">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
@@ -1955,6 +1965,47 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2687,16 +2738,16 @@
         </is>
       </c>
       <c r="B11" s="89" t="n"/>
-      <c r="C11" s="68" t="n"/>
-      <c r="D11" s="93" t="n"/>
-      <c r="E11" s="93" t="n"/>
-      <c r="F11" s="93" t="n"/>
-      <c r="G11" s="93" t="n"/>
-      <c r="H11" s="93" t="n"/>
-      <c r="I11" s="93" t="n"/>
-      <c r="J11" s="93" t="n"/>
-      <c r="K11" s="93" t="n"/>
-      <c r="L11" s="89" t="n"/>
+      <c r="C11" s="366" t="n"/>
+      <c r="D11" s="367" t="n"/>
+      <c r="E11" s="367" t="n"/>
+      <c r="F11" s="367" t="n"/>
+      <c r="G11" s="367" t="n"/>
+      <c r="H11" s="367" t="n"/>
+      <c r="I11" s="367" t="n"/>
+      <c r="J11" s="367" t="n"/>
+      <c r="K11" s="367" t="n"/>
+      <c r="L11" s="368" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1" s="127">
       <c r="A12" s="59" t="inlineStr">
@@ -2705,20 +2756,20 @@
         </is>
       </c>
       <c r="B12" s="89" t="n"/>
-      <c r="C12" s="68" t="n"/>
-      <c r="D12" s="93" t="n"/>
-      <c r="E12" s="93" t="n"/>
-      <c r="F12" s="93" t="n"/>
-      <c r="G12" s="89" t="n"/>
+      <c r="C12" s="366" t="n"/>
+      <c r="D12" s="367" t="n"/>
+      <c r="E12" s="367" t="n"/>
+      <c r="F12" s="367" t="n"/>
+      <c r="G12" s="368" t="n"/>
       <c r="H12" s="59" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
       <c r="I12" s="89" t="n"/>
-      <c r="J12" s="68" t="n"/>
-      <c r="K12" s="93" t="n"/>
-      <c r="L12" s="89" t="n"/>
+      <c r="J12" s="366" t="n"/>
+      <c r="K12" s="367" t="n"/>
+      <c r="L12" s="368" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1" s="127">
       <c r="A13" s="59" t="inlineStr">
@@ -2727,16 +2778,16 @@
         </is>
       </c>
       <c r="B13" s="89" t="n"/>
-      <c r="C13" s="68" t="n"/>
-      <c r="D13" s="93" t="n"/>
-      <c r="E13" s="93" t="n"/>
-      <c r="F13" s="93" t="n"/>
-      <c r="G13" s="93" t="n"/>
-      <c r="H13" s="93" t="n"/>
-      <c r="I13" s="93" t="n"/>
-      <c r="J13" s="93" t="n"/>
-      <c r="K13" s="93" t="n"/>
-      <c r="L13" s="89" t="n"/>
+      <c r="C13" s="366" t="n"/>
+      <c r="D13" s="367" t="n"/>
+      <c r="E13" s="367" t="n"/>
+      <c r="F13" s="367" t="n"/>
+      <c r="G13" s="367" t="n"/>
+      <c r="H13" s="367" t="n"/>
+      <c r="I13" s="367" t="n"/>
+      <c r="J13" s="367" t="n"/>
+      <c r="K13" s="367" t="n"/>
+      <c r="L13" s="368" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1" s="127">
       <c r="A14" s="59" t="inlineStr">
@@ -2745,24 +2796,24 @@
         </is>
       </c>
       <c r="B14" s="89" t="n"/>
-      <c r="C14" s="69" t="n"/>
-      <c r="D14" s="89" t="n"/>
+      <c r="C14" s="369" t="n"/>
+      <c r="D14" s="368" t="n"/>
       <c r="E14" s="59" t="inlineStr">
         <is>
           <t>Vigencia hasta</t>
         </is>
       </c>
       <c r="F14" s="89" t="n"/>
-      <c r="G14" s="69" t="n"/>
-      <c r="H14" s="89" t="n"/>
+      <c r="G14" s="369" t="n"/>
+      <c r="H14" s="368" t="n"/>
       <c r="I14" s="59" t="inlineStr">
         <is>
           <t>Versión del plan</t>
         </is>
       </c>
       <c r="J14" s="89" t="n"/>
-      <c r="K14" s="69" t="n"/>
-      <c r="L14" s="89" t="n"/>
+      <c r="K14" s="369" t="n"/>
+      <c r="L14" s="368" t="n"/>
     </row>
     <row r="15" ht="21" customHeight="1" s="127">
       <c r="A15" s="59" t="inlineStr">
@@ -2771,20 +2822,20 @@
         </is>
       </c>
       <c r="B15" s="89" t="n"/>
-      <c r="C15" s="68" t="n"/>
-      <c r="D15" s="93" t="n"/>
-      <c r="E15" s="93" t="n"/>
-      <c r="F15" s="93" t="n"/>
-      <c r="G15" s="89" t="n"/>
+      <c r="C15" s="366" t="n"/>
+      <c r="D15" s="367" t="n"/>
+      <c r="E15" s="367" t="n"/>
+      <c r="F15" s="367" t="n"/>
+      <c r="G15" s="368" t="n"/>
       <c r="H15" s="59" t="inlineStr">
         <is>
           <t>Teléfono</t>
         </is>
       </c>
       <c r="I15" s="89" t="n"/>
-      <c r="J15" s="68" t="n"/>
-      <c r="K15" s="93" t="n"/>
-      <c r="L15" s="89" t="n"/>
+      <c r="J15" s="366" t="n"/>
+      <c r="K15" s="367" t="n"/>
+      <c r="L15" s="368" t="n"/>
     </row>
     <row r="16" ht="21" customHeight="1" s="127">
       <c r="A16" s="59" t="inlineStr">
@@ -2793,24 +2844,24 @@
         </is>
       </c>
       <c r="B16" s="89" t="n"/>
-      <c r="C16" s="69" t="n"/>
-      <c r="D16" s="89" t="n"/>
+      <c r="C16" s="369" t="n"/>
+      <c r="D16" s="368" t="n"/>
       <c r="E16" s="59" t="inlineStr">
         <is>
           <t>Visitantes por día (aprox.)</t>
         </is>
       </c>
       <c r="F16" s="89" t="n"/>
-      <c r="G16" s="69" t="n"/>
-      <c r="H16" s="89" t="n"/>
+      <c r="G16" s="369" t="n"/>
+      <c r="H16" s="368" t="n"/>
       <c r="I16" s="59" t="inlineStr">
         <is>
           <t>Horario de trabajo</t>
         </is>
       </c>
       <c r="J16" s="89" t="n"/>
-      <c r="K16" s="69" t="n"/>
-      <c r="L16" s="89" t="n"/>
+      <c r="K16" s="369" t="n"/>
+      <c r="L16" s="368" t="n"/>
     </row>
     <row r="17" ht="16.5" customHeight="1" s="127">
       <c r="A17" s="137" t="inlineStr">
@@ -2873,226 +2924,226 @@
       <c r="L18" s="348" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1" s="127">
-      <c r="A19" s="306" t="n">
+      <c r="A19" s="370" t="n">
         <v>1</v>
       </c>
-      <c r="B19" s="230" t="inlineStr">
+      <c r="B19" s="371" t="inlineStr">
         <is>
           <t>Incendio o explosión</t>
         </is>
       </c>
       <c r="C19" s="98" t="n"/>
       <c r="D19" s="97" t="n"/>
-      <c r="E19" s="306" t="n"/>
-      <c r="F19" s="97" t="n"/>
-      <c r="G19" s="306" t="n"/>
-      <c r="H19" s="97" t="n"/>
-      <c r="I19" s="306" t="n"/>
-      <c r="J19" s="362">
+      <c r="E19" s="372" t="n"/>
+      <c r="F19" s="373" t="n"/>
+      <c r="G19" s="372" t="n"/>
+      <c r="H19" s="373" t="n"/>
+      <c r="I19" s="372" t="n"/>
+      <c r="J19" s="374">
         <f>IFERROR(IF(MATCH(G19,{"Posible","Probable","Inminente"},0)*MATCH(I19,{"Bajo","Medio","Alto"},0)&gt;=6,"Alto",IF(MATCH(G19,{"Posible","Probable","Inminente"},0)*MATCH(I19,{"Bajo","Medio","Alto"},0)&gt;=3,"Medio","Bajo")),"")</f>
         <v/>
       </c>
-      <c r="K19" s="230" t="n"/>
-      <c r="L19" s="97" t="n"/>
+      <c r="K19" s="375" t="n"/>
+      <c r="L19" s="373" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1" s="127">
-      <c r="A20" s="306" t="n">
+      <c r="A20" s="370" t="n">
         <v>2</v>
       </c>
-      <c r="B20" s="230" t="inlineStr">
+      <c r="B20" s="371" t="inlineStr">
         <is>
           <t>Sismo</t>
         </is>
       </c>
       <c r="C20" s="98" t="n"/>
       <c r="D20" s="97" t="n"/>
-      <c r="E20" s="306" t="n"/>
-      <c r="F20" s="97" t="n"/>
-      <c r="G20" s="306" t="n"/>
-      <c r="H20" s="97" t="n"/>
-      <c r="I20" s="306" t="n"/>
-      <c r="J20" s="362">
+      <c r="E20" s="372" t="n"/>
+      <c r="F20" s="373" t="n"/>
+      <c r="G20" s="372" t="n"/>
+      <c r="H20" s="373" t="n"/>
+      <c r="I20" s="372" t="n"/>
+      <c r="J20" s="374">
         <f>IFERROR(IF(MATCH(G20,{"Posible","Probable","Inminente"},0)*MATCH(I20,{"Bajo","Medio","Alto"},0)&gt;=6,"Alto",IF(MATCH(G20,{"Posible","Probable","Inminente"},0)*MATCH(I20,{"Bajo","Medio","Alto"},0)&gt;=3,"Medio","Bajo")),"")</f>
         <v/>
       </c>
-      <c r="K20" s="230" t="n"/>
-      <c r="L20" s="97" t="n"/>
+      <c r="K20" s="375" t="n"/>
+      <c r="L20" s="373" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1" s="127">
-      <c r="A21" s="306" t="n">
+      <c r="A21" s="370" t="n">
         <v>3</v>
       </c>
-      <c r="B21" s="230" t="inlineStr">
+      <c r="B21" s="371" t="inlineStr">
         <is>
           <t>Inundación o lluvias fuertes</t>
         </is>
       </c>
       <c r="C21" s="98" t="n"/>
       <c r="D21" s="97" t="n"/>
-      <c r="E21" s="306" t="n"/>
-      <c r="F21" s="97" t="n"/>
-      <c r="G21" s="306" t="n"/>
-      <c r="H21" s="97" t="n"/>
-      <c r="I21" s="306" t="n"/>
-      <c r="J21" s="362">
+      <c r="E21" s="372" t="n"/>
+      <c r="F21" s="373" t="n"/>
+      <c r="G21" s="372" t="n"/>
+      <c r="H21" s="373" t="n"/>
+      <c r="I21" s="372" t="n"/>
+      <c r="J21" s="374">
         <f>IFERROR(IF(MATCH(G21,{"Posible","Probable","Inminente"},0)*MATCH(I21,{"Bajo","Medio","Alto"},0)&gt;=6,"Alto",IF(MATCH(G21,{"Posible","Probable","Inminente"},0)*MATCH(I21,{"Bajo","Medio","Alto"},0)&gt;=3,"Medio","Bajo")),"")</f>
         <v/>
       </c>
-      <c r="K21" s="230" t="n"/>
-      <c r="L21" s="97" t="n"/>
+      <c r="K21" s="375" t="n"/>
+      <c r="L21" s="373" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1" s="127">
-      <c r="A22" s="306" t="n">
+      <c r="A22" s="370" t="n">
         <v>4</v>
       </c>
-      <c r="B22" s="230" t="inlineStr">
+      <c r="B22" s="371" t="inlineStr">
         <is>
           <t>Caída de personas a distinto nivel</t>
         </is>
       </c>
       <c r="C22" s="98" t="n"/>
       <c r="D22" s="97" t="n"/>
-      <c r="E22" s="306" t="n"/>
-      <c r="F22" s="97" t="n"/>
-      <c r="G22" s="306" t="n"/>
-      <c r="H22" s="97" t="n"/>
-      <c r="I22" s="306" t="n"/>
-      <c r="J22" s="362">
+      <c r="E22" s="372" t="n"/>
+      <c r="F22" s="373" t="n"/>
+      <c r="G22" s="372" t="n"/>
+      <c r="H22" s="373" t="n"/>
+      <c r="I22" s="372" t="n"/>
+      <c r="J22" s="374">
         <f>IFERROR(IF(MATCH(G22,{"Posible","Probable","Inminente"},0)*MATCH(I22,{"Bajo","Medio","Alto"},0)&gt;=6,"Alto",IF(MATCH(G22,{"Posible","Probable","Inminente"},0)*MATCH(I22,{"Bajo","Medio","Alto"},0)&gt;=3,"Medio","Bajo")),"")</f>
         <v/>
       </c>
-      <c r="K22" s="230" t="n"/>
-      <c r="L22" s="97" t="n"/>
+      <c r="K22" s="375" t="n"/>
+      <c r="L22" s="373" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1" s="127">
-      <c r="A23" s="306" t="n">
+      <c r="A23" s="370" t="n">
         <v>5</v>
       </c>
-      <c r="B23" s="230" t="inlineStr">
+      <c r="B23" s="371" t="inlineStr">
         <is>
           <t>Derrumbe o colapso de estructura o excavación</t>
         </is>
       </c>
       <c r="C23" s="98" t="n"/>
       <c r="D23" s="97" t="n"/>
-      <c r="E23" s="306" t="n"/>
-      <c r="F23" s="97" t="n"/>
-      <c r="G23" s="306" t="n"/>
-      <c r="H23" s="97" t="n"/>
-      <c r="I23" s="306" t="n"/>
-      <c r="J23" s="362">
+      <c r="E23" s="372" t="n"/>
+      <c r="F23" s="373" t="n"/>
+      <c r="G23" s="372" t="n"/>
+      <c r="H23" s="373" t="n"/>
+      <c r="I23" s="372" t="n"/>
+      <c r="J23" s="374">
         <f>IFERROR(IF(MATCH(G23,{"Posible","Probable","Inminente"},0)*MATCH(I23,{"Bajo","Medio","Alto"},0)&gt;=6,"Alto",IF(MATCH(G23,{"Posible","Probable","Inminente"},0)*MATCH(I23,{"Bajo","Medio","Alto"},0)&gt;=3,"Medio","Bajo")),"")</f>
         <v/>
       </c>
-      <c r="K23" s="230" t="n"/>
-      <c r="L23" s="97" t="n"/>
+      <c r="K23" s="375" t="n"/>
+      <c r="L23" s="373" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1" s="127">
-      <c r="A24" s="306" t="n">
+      <c r="A24" s="370" t="n">
         <v>6</v>
       </c>
-      <c r="B24" s="230" t="inlineStr">
+      <c r="B24" s="371" t="inlineStr">
         <is>
           <t>Descarga eléctrica</t>
         </is>
       </c>
       <c r="C24" s="98" t="n"/>
       <c r="D24" s="97" t="n"/>
-      <c r="E24" s="306" t="n"/>
-      <c r="F24" s="97" t="n"/>
-      <c r="G24" s="306" t="n"/>
-      <c r="H24" s="97" t="n"/>
-      <c r="I24" s="306" t="n"/>
-      <c r="J24" s="362">
+      <c r="E24" s="372" t="n"/>
+      <c r="F24" s="373" t="n"/>
+      <c r="G24" s="372" t="n"/>
+      <c r="H24" s="373" t="n"/>
+      <c r="I24" s="372" t="n"/>
+      <c r="J24" s="374">
         <f>IFERROR(IF(MATCH(G24,{"Posible","Probable","Inminente"},0)*MATCH(I24,{"Bajo","Medio","Alto"},0)&gt;=6,"Alto",IF(MATCH(G24,{"Posible","Probable","Inminente"},0)*MATCH(I24,{"Bajo","Medio","Alto"},0)&gt;=3,"Medio","Bajo")),"")</f>
         <v/>
       </c>
-      <c r="K24" s="230" t="n"/>
-      <c r="L24" s="97" t="n"/>
+      <c r="K24" s="375" t="n"/>
+      <c r="L24" s="373" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1" s="127">
-      <c r="A25" s="306" t="n">
+      <c r="A25" s="370" t="n">
         <v>7</v>
       </c>
-      <c r="B25" s="230" t="inlineStr">
+      <c r="B25" s="371" t="inlineStr">
         <is>
           <t>Derrame o fuga de sustancias peligrosas</t>
         </is>
       </c>
       <c r="C25" s="98" t="n"/>
       <c r="D25" s="97" t="n"/>
-      <c r="E25" s="306" t="n"/>
-      <c r="F25" s="97" t="n"/>
-      <c r="G25" s="306" t="n"/>
-      <c r="H25" s="97" t="n"/>
-      <c r="I25" s="306" t="n"/>
-      <c r="J25" s="362">
+      <c r="E25" s="372" t="n"/>
+      <c r="F25" s="373" t="n"/>
+      <c r="G25" s="372" t="n"/>
+      <c r="H25" s="373" t="n"/>
+      <c r="I25" s="372" t="n"/>
+      <c r="J25" s="374">
         <f>IFERROR(IF(MATCH(G25,{"Posible","Probable","Inminente"},0)*MATCH(I25,{"Bajo","Medio","Alto"},0)&gt;=6,"Alto",IF(MATCH(G25,{"Posible","Probable","Inminente"},0)*MATCH(I25,{"Bajo","Medio","Alto"},0)&gt;=3,"Medio","Bajo")),"")</f>
         <v/>
       </c>
-      <c r="K25" s="230" t="n"/>
-      <c r="L25" s="97" t="n"/>
+      <c r="K25" s="375" t="n"/>
+      <c r="L25" s="373" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1" s="127">
-      <c r="A26" s="306" t="n">
+      <c r="A26" s="370" t="n">
         <v>8</v>
       </c>
-      <c r="B26" s="230" t="inlineStr">
+      <c r="B26" s="371" t="inlineStr">
         <is>
           <t>Accidente de tránsito dentro de la obra</t>
         </is>
       </c>
       <c r="C26" s="98" t="n"/>
       <c r="D26" s="97" t="n"/>
-      <c r="E26" s="306" t="n"/>
-      <c r="F26" s="97" t="n"/>
-      <c r="G26" s="306" t="n"/>
-      <c r="H26" s="97" t="n"/>
-      <c r="I26" s="306" t="n"/>
-      <c r="J26" s="362">
+      <c r="E26" s="372" t="n"/>
+      <c r="F26" s="373" t="n"/>
+      <c r="G26" s="372" t="n"/>
+      <c r="H26" s="373" t="n"/>
+      <c r="I26" s="372" t="n"/>
+      <c r="J26" s="374">
         <f>IFERROR(IF(MATCH(G26,{"Posible","Probable","Inminente"},0)*MATCH(I26,{"Bajo","Medio","Alto"},0)&gt;=6,"Alto",IF(MATCH(G26,{"Posible","Probable","Inminente"},0)*MATCH(I26,{"Bajo","Medio","Alto"},0)&gt;=3,"Medio","Bajo")),"")</f>
         <v/>
       </c>
-      <c r="K26" s="230" t="n"/>
-      <c r="L26" s="97" t="n"/>
+      <c r="K26" s="375" t="n"/>
+      <c r="L26" s="373" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1" s="127">
-      <c r="A27" s="306" t="n">
+      <c r="A27" s="370" t="n">
         <v>9</v>
       </c>
-      <c r="B27" s="230" t="n"/>
-      <c r="C27" s="98" t="n"/>
-      <c r="D27" s="97" t="n"/>
-      <c r="E27" s="306" t="n"/>
-      <c r="F27" s="97" t="n"/>
-      <c r="G27" s="306" t="n"/>
-      <c r="H27" s="97" t="n"/>
-      <c r="I27" s="306" t="n"/>
-      <c r="J27" s="362">
+      <c r="B27" s="375" t="n"/>
+      <c r="C27" s="376" t="n"/>
+      <c r="D27" s="373" t="n"/>
+      <c r="E27" s="372" t="n"/>
+      <c r="F27" s="373" t="n"/>
+      <c r="G27" s="372" t="n"/>
+      <c r="H27" s="373" t="n"/>
+      <c r="I27" s="372" t="n"/>
+      <c r="J27" s="374">
         <f>IFERROR(IF(MATCH(G27,{"Posible","Probable","Inminente"},0)*MATCH(I27,{"Bajo","Medio","Alto"},0)&gt;=6,"Alto",IF(MATCH(G27,{"Posible","Probable","Inminente"},0)*MATCH(I27,{"Bajo","Medio","Alto"},0)&gt;=3,"Medio","Bajo")),"")</f>
         <v/>
       </c>
-      <c r="K27" s="230" t="n"/>
-      <c r="L27" s="97" t="n"/>
+      <c r="K27" s="375" t="n"/>
+      <c r="L27" s="373" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1" s="127">
-      <c r="A28" s="306" t="n">
+      <c r="A28" s="370" t="n">
         <v>10</v>
       </c>
-      <c r="B28" s="230" t="n"/>
-      <c r="C28" s="98" t="n"/>
-      <c r="D28" s="97" t="n"/>
-      <c r="E28" s="306" t="n"/>
-      <c r="F28" s="97" t="n"/>
-      <c r="G28" s="306" t="n"/>
-      <c r="H28" s="97" t="n"/>
-      <c r="I28" s="306" t="n"/>
-      <c r="J28" s="362">
+      <c r="B28" s="375" t="n"/>
+      <c r="C28" s="376" t="n"/>
+      <c r="D28" s="373" t="n"/>
+      <c r="E28" s="372" t="n"/>
+      <c r="F28" s="373" t="n"/>
+      <c r="G28" s="372" t="n"/>
+      <c r="H28" s="373" t="n"/>
+      <c r="I28" s="372" t="n"/>
+      <c r="J28" s="374">
         <f>IFERROR(IF(MATCH(G28,{"Posible","Probable","Inminente"},0)*MATCH(I28,{"Bajo","Medio","Alto"},0)&gt;=6,"Alto",IF(MATCH(G28,{"Posible","Probable","Inminente"},0)*MATCH(I28,{"Bajo","Medio","Alto"},0)&gt;=3,"Medio","Bajo")),"")</f>
         <v/>
       </c>
-      <c r="K28" s="230" t="n"/>
-      <c r="L28" s="97" t="n"/>
+      <c r="K28" s="375" t="n"/>
+      <c r="L28" s="373" t="n"/>
     </row>
     <row r="29" ht="16.5" customHeight="1" s="127">
       <c r="A29" s="137" t="inlineStr">
@@ -3147,104 +3198,104 @@
       <c r="L30" s="348" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1" s="127">
-      <c r="A31" s="306" t="n">
+      <c r="A31" s="370" t="n">
         <v>1</v>
       </c>
-      <c r="B31" s="230" t="inlineStr">
+      <c r="B31" s="371" t="inlineStr">
         <is>
           <t>Jefe de brigada</t>
         </is>
       </c>
       <c r="C31" s="98" t="n"/>
       <c r="D31" s="97" t="n"/>
-      <c r="E31" s="230" t="n"/>
-      <c r="F31" s="98" t="n"/>
-      <c r="G31" s="97" t="n"/>
-      <c r="H31" s="306" t="n"/>
-      <c r="I31" s="97" t="n"/>
-      <c r="J31" s="230" t="n"/>
-      <c r="K31" s="98" t="n"/>
-      <c r="L31" s="97" t="n"/>
+      <c r="E31" s="375" t="n"/>
+      <c r="F31" s="376" t="n"/>
+      <c r="G31" s="373" t="n"/>
+      <c r="H31" s="372" t="n"/>
+      <c r="I31" s="373" t="n"/>
+      <c r="J31" s="375" t="n"/>
+      <c r="K31" s="376" t="n"/>
+      <c r="L31" s="373" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1" s="127">
-      <c r="A32" s="306" t="n">
+      <c r="A32" s="370" t="n">
         <v>2</v>
       </c>
-      <c r="B32" s="230" t="inlineStr">
+      <c r="B32" s="371" t="inlineStr">
         <is>
           <t>Primeros auxilios</t>
         </is>
       </c>
       <c r="C32" s="98" t="n"/>
       <c r="D32" s="97" t="n"/>
-      <c r="E32" s="230" t="n"/>
-      <c r="F32" s="98" t="n"/>
-      <c r="G32" s="97" t="n"/>
-      <c r="H32" s="306" t="n"/>
-      <c r="I32" s="97" t="n"/>
-      <c r="J32" s="230" t="n"/>
-      <c r="K32" s="98" t="n"/>
-      <c r="L32" s="97" t="n"/>
+      <c r="E32" s="375" t="n"/>
+      <c r="F32" s="376" t="n"/>
+      <c r="G32" s="373" t="n"/>
+      <c r="H32" s="372" t="n"/>
+      <c r="I32" s="373" t="n"/>
+      <c r="J32" s="375" t="n"/>
+      <c r="K32" s="376" t="n"/>
+      <c r="L32" s="373" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1" s="127">
-      <c r="A33" s="306" t="n">
+      <c r="A33" s="370" t="n">
         <v>3</v>
       </c>
-      <c r="B33" s="230" t="inlineStr">
+      <c r="B33" s="371" t="inlineStr">
         <is>
           <t>Control de incendios</t>
         </is>
       </c>
       <c r="C33" s="98" t="n"/>
       <c r="D33" s="97" t="n"/>
-      <c r="E33" s="230" t="n"/>
-      <c r="F33" s="98" t="n"/>
-      <c r="G33" s="97" t="n"/>
-      <c r="H33" s="306" t="n"/>
-      <c r="I33" s="97" t="n"/>
-      <c r="J33" s="230" t="n"/>
-      <c r="K33" s="98" t="n"/>
-      <c r="L33" s="97" t="n"/>
+      <c r="E33" s="375" t="n"/>
+      <c r="F33" s="376" t="n"/>
+      <c r="G33" s="373" t="n"/>
+      <c r="H33" s="372" t="n"/>
+      <c r="I33" s="373" t="n"/>
+      <c r="J33" s="375" t="n"/>
+      <c r="K33" s="376" t="n"/>
+      <c r="L33" s="373" t="n"/>
     </row>
     <row r="34" ht="20" customHeight="1" s="127">
-      <c r="A34" s="306" t="n">
+      <c r="A34" s="370" t="n">
         <v>4</v>
       </c>
-      <c r="B34" s="230" t="inlineStr">
+      <c r="B34" s="371" t="inlineStr">
         <is>
           <t>Evacuación y rescate</t>
         </is>
       </c>
       <c r="C34" s="98" t="n"/>
       <c r="D34" s="97" t="n"/>
-      <c r="E34" s="230" t="n"/>
-      <c r="F34" s="98" t="n"/>
-      <c r="G34" s="97" t="n"/>
-      <c r="H34" s="306" t="n"/>
-      <c r="I34" s="97" t="n"/>
-      <c r="J34" s="230" t="n"/>
-      <c r="K34" s="98" t="n"/>
-      <c r="L34" s="97" t="n"/>
+      <c r="E34" s="375" t="n"/>
+      <c r="F34" s="376" t="n"/>
+      <c r="G34" s="373" t="n"/>
+      <c r="H34" s="372" t="n"/>
+      <c r="I34" s="373" t="n"/>
+      <c r="J34" s="375" t="n"/>
+      <c r="K34" s="376" t="n"/>
+      <c r="L34" s="373" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1" s="127">
-      <c r="A35" s="306" t="n">
+      <c r="A35" s="370" t="n">
         <v>5</v>
       </c>
-      <c r="B35" s="230" t="inlineStr">
+      <c r="B35" s="371" t="inlineStr">
         <is>
           <t>Comunicaciones</t>
         </is>
       </c>
       <c r="C35" s="98" t="n"/>
       <c r="D35" s="97" t="n"/>
-      <c r="E35" s="230" t="n"/>
-      <c r="F35" s="98" t="n"/>
-      <c r="G35" s="97" t="n"/>
-      <c r="H35" s="306" t="n"/>
-      <c r="I35" s="97" t="n"/>
-      <c r="J35" s="230" t="n"/>
-      <c r="K35" s="98" t="n"/>
-      <c r="L35" s="97" t="n"/>
+      <c r="E35" s="375" t="n"/>
+      <c r="F35" s="376" t="n"/>
+      <c r="G35" s="373" t="n"/>
+      <c r="H35" s="372" t="n"/>
+      <c r="I35" s="373" t="n"/>
+      <c r="J35" s="375" t="n"/>
+      <c r="K35" s="376" t="n"/>
+      <c r="L35" s="373" t="n"/>
     </row>
     <row r="36" ht="16.5" customHeight="1" s="127">
       <c r="A36" s="137" t="inlineStr">
@@ -3271,16 +3322,16 @@
         </is>
       </c>
       <c r="B37" s="89" t="n"/>
-      <c r="C37" s="365" t="n"/>
-      <c r="D37" s="93" t="n"/>
-      <c r="E37" s="93" t="n"/>
-      <c r="F37" s="93" t="n"/>
-      <c r="G37" s="93" t="n"/>
-      <c r="H37" s="93" t="n"/>
-      <c r="I37" s="93" t="n"/>
-      <c r="J37" s="93" t="n"/>
-      <c r="K37" s="93" t="n"/>
-      <c r="L37" s="89" t="n"/>
+      <c r="C37" s="366" t="n"/>
+      <c r="D37" s="367" t="n"/>
+      <c r="E37" s="367" t="n"/>
+      <c r="F37" s="367" t="n"/>
+      <c r="G37" s="367" t="n"/>
+      <c r="H37" s="367" t="n"/>
+      <c r="I37" s="367" t="n"/>
+      <c r="J37" s="367" t="n"/>
+      <c r="K37" s="367" t="n"/>
+      <c r="L37" s="368" t="n"/>
     </row>
     <row r="38" ht="30" customHeight="1" s="127">
       <c r="A38" s="59" t="inlineStr">
@@ -3289,16 +3340,16 @@
         </is>
       </c>
       <c r="B38" s="89" t="n"/>
-      <c r="C38" s="365" t="n"/>
-      <c r="D38" s="93" t="n"/>
-      <c r="E38" s="93" t="n"/>
-      <c r="F38" s="93" t="n"/>
-      <c r="G38" s="93" t="n"/>
-      <c r="H38" s="93" t="n"/>
-      <c r="I38" s="93" t="n"/>
-      <c r="J38" s="93" t="n"/>
-      <c r="K38" s="93" t="n"/>
-      <c r="L38" s="89" t="n"/>
+      <c r="C38" s="366" t="n"/>
+      <c r="D38" s="367" t="n"/>
+      <c r="E38" s="367" t="n"/>
+      <c r="F38" s="367" t="n"/>
+      <c r="G38" s="367" t="n"/>
+      <c r="H38" s="367" t="n"/>
+      <c r="I38" s="367" t="n"/>
+      <c r="J38" s="367" t="n"/>
+      <c r="K38" s="367" t="n"/>
+      <c r="L38" s="368" t="n"/>
     </row>
     <row r="39" ht="21" customHeight="1" s="127">
       <c r="A39" s="59" t="inlineStr">
@@ -3307,20 +3358,20 @@
         </is>
       </c>
       <c r="B39" s="89" t="n"/>
-      <c r="C39" s="68" t="n"/>
-      <c r="D39" s="93" t="n"/>
-      <c r="E39" s="93" t="n"/>
-      <c r="F39" s="93" t="n"/>
-      <c r="G39" s="89" t="n"/>
+      <c r="C39" s="366" t="n"/>
+      <c r="D39" s="367" t="n"/>
+      <c r="E39" s="367" t="n"/>
+      <c r="F39" s="367" t="n"/>
+      <c r="G39" s="368" t="n"/>
       <c r="H39" s="59" t="inlineStr">
         <is>
           <t>Botiquines (N°)</t>
         </is>
       </c>
       <c r="I39" s="89" t="n"/>
-      <c r="J39" s="69" t="n"/>
-      <c r="K39" s="93" t="n"/>
-      <c r="L39" s="89" t="n"/>
+      <c r="J39" s="369" t="n"/>
+      <c r="K39" s="367" t="n"/>
+      <c r="L39" s="368" t="n"/>
     </row>
     <row r="40" ht="21" customHeight="1" s="127">
       <c r="A40" s="59" t="inlineStr">
@@ -3329,20 +3380,20 @@
         </is>
       </c>
       <c r="B40" s="89" t="n"/>
-      <c r="C40" s="69" t="n"/>
-      <c r="D40" s="93" t="n"/>
-      <c r="E40" s="93" t="n"/>
-      <c r="F40" s="93" t="n"/>
-      <c r="G40" s="89" t="n"/>
+      <c r="C40" s="369" t="n"/>
+      <c r="D40" s="367" t="n"/>
+      <c r="E40" s="367" t="n"/>
+      <c r="F40" s="367" t="n"/>
+      <c r="G40" s="368" t="n"/>
       <c r="H40" s="59" t="inlineStr">
         <is>
           <t>Alarma o aviso</t>
         </is>
       </c>
       <c r="I40" s="89" t="n"/>
-      <c r="J40" s="68" t="n"/>
-      <c r="K40" s="93" t="n"/>
-      <c r="L40" s="89" t="n"/>
+      <c r="J40" s="366" t="n"/>
+      <c r="K40" s="367" t="n"/>
+      <c r="L40" s="368" t="n"/>
     </row>
     <row r="41" ht="21" customHeight="1" s="127">
       <c r="A41" s="59" t="inlineStr">
@@ -3351,20 +3402,20 @@
         </is>
       </c>
       <c r="B41" s="89" t="n"/>
-      <c r="C41" s="69" t="n"/>
-      <c r="D41" s="93" t="n"/>
-      <c r="E41" s="93" t="n"/>
-      <c r="F41" s="93" t="n"/>
-      <c r="G41" s="89" t="n"/>
+      <c r="C41" s="369" t="n"/>
+      <c r="D41" s="367" t="n"/>
+      <c r="E41" s="367" t="n"/>
+      <c r="F41" s="367" t="n"/>
+      <c r="G41" s="368" t="n"/>
       <c r="H41" s="59" t="inlineStr">
         <is>
           <t>Centro médico más cercano</t>
         </is>
       </c>
       <c r="I41" s="89" t="n"/>
-      <c r="J41" s="68" t="n"/>
-      <c r="K41" s="93" t="n"/>
-      <c r="L41" s="89" t="n"/>
+      <c r="J41" s="366" t="n"/>
+      <c r="K41" s="367" t="n"/>
+      <c r="L41" s="368" t="n"/>
     </row>
     <row r="42" ht="16.5" customHeight="1" s="127">
       <c r="A42" s="137" t="inlineStr">
@@ -3391,16 +3442,16 @@
         </is>
       </c>
       <c r="B43" s="89" t="n"/>
-      <c r="C43" s="100" t="n"/>
-      <c r="D43" s="93" t="n"/>
-      <c r="E43" s="93" t="n"/>
-      <c r="F43" s="93" t="n"/>
-      <c r="G43" s="93" t="n"/>
-      <c r="H43" s="93" t="n"/>
-      <c r="I43" s="93" t="n"/>
-      <c r="J43" s="93" t="n"/>
-      <c r="K43" s="93" t="n"/>
-      <c r="L43" s="89" t="n"/>
+      <c r="C43" s="377" t="n"/>
+      <c r="D43" s="367" t="n"/>
+      <c r="E43" s="367" t="n"/>
+      <c r="F43" s="367" t="n"/>
+      <c r="G43" s="367" t="n"/>
+      <c r="H43" s="367" t="n"/>
+      <c r="I43" s="367" t="n"/>
+      <c r="J43" s="367" t="n"/>
+      <c r="K43" s="367" t="n"/>
+      <c r="L43" s="368" t="n"/>
     </row>
     <row r="44" ht="46" customHeight="1" s="127">
       <c r="A44" s="59" t="inlineStr">
@@ -3409,16 +3460,16 @@
         </is>
       </c>
       <c r="B44" s="89" t="n"/>
-      <c r="C44" s="100" t="n"/>
-      <c r="D44" s="93" t="n"/>
-      <c r="E44" s="93" t="n"/>
-      <c r="F44" s="93" t="n"/>
-      <c r="G44" s="93" t="n"/>
-      <c r="H44" s="93" t="n"/>
-      <c r="I44" s="93" t="n"/>
-      <c r="J44" s="93" t="n"/>
-      <c r="K44" s="93" t="n"/>
-      <c r="L44" s="89" t="n"/>
+      <c r="C44" s="377" t="n"/>
+      <c r="D44" s="367" t="n"/>
+      <c r="E44" s="367" t="n"/>
+      <c r="F44" s="367" t="n"/>
+      <c r="G44" s="367" t="n"/>
+      <c r="H44" s="367" t="n"/>
+      <c r="I44" s="367" t="n"/>
+      <c r="J44" s="367" t="n"/>
+      <c r="K44" s="367" t="n"/>
+      <c r="L44" s="368" t="n"/>
     </row>
     <row r="45" ht="46" customHeight="1" s="127">
       <c r="A45" s="59" t="inlineStr">
@@ -3427,16 +3478,16 @@
         </is>
       </c>
       <c r="B45" s="89" t="n"/>
-      <c r="C45" s="100" t="n"/>
-      <c r="D45" s="93" t="n"/>
-      <c r="E45" s="93" t="n"/>
-      <c r="F45" s="93" t="n"/>
-      <c r="G45" s="93" t="n"/>
-      <c r="H45" s="93" t="n"/>
-      <c r="I45" s="93" t="n"/>
-      <c r="J45" s="93" t="n"/>
-      <c r="K45" s="93" t="n"/>
-      <c r="L45" s="89" t="n"/>
+      <c r="C45" s="377" t="n"/>
+      <c r="D45" s="367" t="n"/>
+      <c r="E45" s="367" t="n"/>
+      <c r="F45" s="367" t="n"/>
+      <c r="G45" s="367" t="n"/>
+      <c r="H45" s="367" t="n"/>
+      <c r="I45" s="367" t="n"/>
+      <c r="J45" s="367" t="n"/>
+      <c r="K45" s="367" t="n"/>
+      <c r="L45" s="368" t="n"/>
     </row>
     <row r="46" ht="16.5" customHeight="1" s="127">
       <c r="A46" s="137" t="inlineStr">
@@ -3495,68 +3546,68 @@
       <c r="L47" s="348" t="n"/>
     </row>
     <row r="48" ht="24" customHeight="1" s="127">
-      <c r="A48" s="306" t="n">
+      <c r="A48" s="370" t="n">
         <v>1</v>
       </c>
-      <c r="B48" s="306" t="n"/>
-      <c r="C48" s="97" t="n"/>
-      <c r="D48" s="230" t="n"/>
-      <c r="E48" s="98" t="n"/>
-      <c r="F48" s="97" t="n"/>
-      <c r="G48" s="306" t="n"/>
-      <c r="H48" s="306" t="n"/>
-      <c r="I48" s="230" t="n"/>
-      <c r="J48" s="98" t="n"/>
-      <c r="K48" s="98" t="n"/>
-      <c r="L48" s="97" t="n"/>
+      <c r="B48" s="372" t="n"/>
+      <c r="C48" s="373" t="n"/>
+      <c r="D48" s="375" t="n"/>
+      <c r="E48" s="376" t="n"/>
+      <c r="F48" s="373" t="n"/>
+      <c r="G48" s="372" t="n"/>
+      <c r="H48" s="372" t="n"/>
+      <c r="I48" s="375" t="n"/>
+      <c r="J48" s="376" t="n"/>
+      <c r="K48" s="376" t="n"/>
+      <c r="L48" s="373" t="n"/>
     </row>
     <row r="49" ht="24" customHeight="1" s="127">
-      <c r="A49" s="306" t="n">
+      <c r="A49" s="370" t="n">
         <v>2</v>
       </c>
-      <c r="B49" s="306" t="n"/>
-      <c r="C49" s="97" t="n"/>
-      <c r="D49" s="230" t="n"/>
-      <c r="E49" s="98" t="n"/>
-      <c r="F49" s="97" t="n"/>
-      <c r="G49" s="306" t="n"/>
-      <c r="H49" s="306" t="n"/>
-      <c r="I49" s="230" t="n"/>
-      <c r="J49" s="98" t="n"/>
-      <c r="K49" s="98" t="n"/>
-      <c r="L49" s="97" t="n"/>
+      <c r="B49" s="372" t="n"/>
+      <c r="C49" s="373" t="n"/>
+      <c r="D49" s="375" t="n"/>
+      <c r="E49" s="376" t="n"/>
+      <c r="F49" s="373" t="n"/>
+      <c r="G49" s="372" t="n"/>
+      <c r="H49" s="372" t="n"/>
+      <c r="I49" s="375" t="n"/>
+      <c r="J49" s="376" t="n"/>
+      <c r="K49" s="376" t="n"/>
+      <c r="L49" s="373" t="n"/>
     </row>
     <row r="50" ht="24" customHeight="1" s="127">
-      <c r="A50" s="306" t="n">
+      <c r="A50" s="370" t="n">
         <v>3</v>
       </c>
-      <c r="B50" s="306" t="n"/>
-      <c r="C50" s="97" t="n"/>
-      <c r="D50" s="230" t="n"/>
-      <c r="E50" s="98" t="n"/>
-      <c r="F50" s="97" t="n"/>
-      <c r="G50" s="306" t="n"/>
-      <c r="H50" s="306" t="n"/>
-      <c r="I50" s="230" t="n"/>
-      <c r="J50" s="98" t="n"/>
-      <c r="K50" s="98" t="n"/>
-      <c r="L50" s="97" t="n"/>
+      <c r="B50" s="372" t="n"/>
+      <c r="C50" s="373" t="n"/>
+      <c r="D50" s="375" t="n"/>
+      <c r="E50" s="376" t="n"/>
+      <c r="F50" s="373" t="n"/>
+      <c r="G50" s="372" t="n"/>
+      <c r="H50" s="372" t="n"/>
+      <c r="I50" s="375" t="n"/>
+      <c r="J50" s="376" t="n"/>
+      <c r="K50" s="376" t="n"/>
+      <c r="L50" s="373" t="n"/>
     </row>
     <row r="51" ht="24" customHeight="1" s="127">
-      <c r="A51" s="306" t="n">
+      <c r="A51" s="370" t="n">
         <v>4</v>
       </c>
-      <c r="B51" s="306" t="n"/>
-      <c r="C51" s="97" t="n"/>
-      <c r="D51" s="230" t="n"/>
-      <c r="E51" s="98" t="n"/>
-      <c r="F51" s="97" t="n"/>
-      <c r="G51" s="306" t="n"/>
-      <c r="H51" s="306" t="n"/>
-      <c r="I51" s="230" t="n"/>
-      <c r="J51" s="98" t="n"/>
-      <c r="K51" s="98" t="n"/>
-      <c r="L51" s="97" t="n"/>
+      <c r="B51" s="372" t="n"/>
+      <c r="C51" s="373" t="n"/>
+      <c r="D51" s="375" t="n"/>
+      <c r="E51" s="376" t="n"/>
+      <c r="F51" s="373" t="n"/>
+      <c r="G51" s="372" t="n"/>
+      <c r="H51" s="372" t="n"/>
+      <c r="I51" s="375" t="n"/>
+      <c r="J51" s="376" t="n"/>
+      <c r="K51" s="376" t="n"/>
+      <c r="L51" s="373" t="n"/>
     </row>
     <row r="52" ht="16.5" customHeight="1" s="127">
       <c r="A52" s="137" t="inlineStr">
@@ -3609,24 +3660,24 @@
         </is>
       </c>
       <c r="B54" s="97" t="n"/>
-      <c r="C54" s="301" t="n"/>
-      <c r="D54" s="97" t="n"/>
+      <c r="C54" s="375" t="n"/>
+      <c r="D54" s="373" t="n"/>
       <c r="E54" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F54" s="97" t="n"/>
-      <c r="G54" s="301" t="n"/>
-      <c r="H54" s="97" t="n"/>
+      <c r="G54" s="375" t="n"/>
+      <c r="H54" s="373" t="n"/>
       <c r="I54" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="J54" s="97" t="n"/>
-      <c r="K54" s="301" t="n"/>
-      <c r="L54" s="97" t="n"/>
+      <c r="K54" s="375" t="n"/>
+      <c r="L54" s="373" t="n"/>
     </row>
     <row r="55" ht="21" customHeight="1" s="127">
       <c r="A55" s="302" t="inlineStr">
@@ -3635,24 +3686,24 @@
         </is>
       </c>
       <c r="B55" s="97" t="n"/>
-      <c r="C55" s="301" t="n"/>
-      <c r="D55" s="97" t="n"/>
+      <c r="C55" s="375" t="n"/>
+      <c r="D55" s="373" t="n"/>
       <c r="E55" s="302" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="F55" s="97" t="n"/>
-      <c r="G55" s="301" t="n"/>
-      <c r="H55" s="97" t="n"/>
+      <c r="G55" s="375" t="n"/>
+      <c r="H55" s="373" t="n"/>
       <c r="I55" s="302" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="J55" s="97" t="n"/>
-      <c r="K55" s="301" t="n"/>
-      <c r="L55" s="97" t="n"/>
+      <c r="K55" s="375" t="n"/>
+      <c r="L55" s="373" t="n"/>
     </row>
     <row r="56" ht="21" customHeight="1" s="127">
       <c r="A56" s="302" t="inlineStr">
@@ -3661,24 +3712,24 @@
         </is>
       </c>
       <c r="B56" s="97" t="n"/>
-      <c r="C56" s="301" t="n"/>
-      <c r="D56" s="97" t="n"/>
+      <c r="C56" s="375" t="n"/>
+      <c r="D56" s="373" t="n"/>
       <c r="E56" s="302" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="F56" s="97" t="n"/>
-      <c r="G56" s="301" t="n"/>
-      <c r="H56" s="97" t="n"/>
+      <c r="G56" s="375" t="n"/>
+      <c r="H56" s="373" t="n"/>
       <c r="I56" s="302" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="J56" s="97" t="n"/>
-      <c r="K56" s="301" t="n"/>
-      <c r="L56" s="97" t="n"/>
+      <c r="K56" s="375" t="n"/>
+      <c r="L56" s="373" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="25" t="inlineStr">
@@ -3692,6 +3743,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="168">
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="H35:I35"/>
